--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -455,13 +455,13 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>16.70811</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.48738</v>
+      </c>
+      <c r="E2" t="n">
         <v>16.63399</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16.70811</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16.48738</v>
       </c>
       <c r="F2" t="n">
         <v>42.37345</v>
@@ -508,10 +508,10 @@
         <v>16.72589</v>
       </c>
       <c r="D4" t="n">
+        <v>16.42584</v>
+      </c>
+      <c r="E4" t="n">
         <v>16.61018</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.42584</v>
       </c>
       <c r="F4" t="n">
         <v>42.37896</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>16.98683</v>
+      </c>
+      <c r="D5" t="n">
         <v>16.64198</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>16.76516</v>
-      </c>
-      <c r="E5" t="n">
-        <v>16.98683</v>
       </c>
       <c r="F5" t="n">
         <v>42.09761</v>
@@ -558,10 +558,10 @@
         <v>16.92131</v>
       </c>
       <c r="D6" t="n">
+        <v>16.3294</v>
+      </c>
+      <c r="E6" t="n">
         <v>16.65107</v>
-      </c>
-      <c r="E6" t="n">
-        <v>16.3294</v>
       </c>
       <c r="F6" t="n">
         <v>42.46421</v>
@@ -583,10 +583,10 @@
         <v>16.5416</v>
       </c>
       <c r="D7" t="n">
+        <v>16.39145</v>
+      </c>
+      <c r="E7" t="n">
         <v>16.39851</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.39145</v>
       </c>
       <c r="F7" t="n">
         <v>41.25945</v>
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.42027</v>
+        <v>16.78712</v>
       </c>
       <c r="D8" t="n">
         <v>16.05512</v>
       </c>
       <c r="E8" t="n">
-        <v>16.78712</v>
+        <v>16.42027</v>
       </c>
       <c r="F8" t="n">
         <v>42.70665</v>
@@ -658,10 +658,10 @@
         <v>16.73824</v>
       </c>
       <c r="D10" t="n">
+        <v>16.0228</v>
+      </c>
+      <c r="E10" t="n">
         <v>16.59827</v>
-      </c>
-      <c r="E10" t="n">
-        <v>16.0228</v>
       </c>
       <c r="F10" t="n">
         <v>42.71323</v>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.60597</v>
+        <v>16.62076</v>
       </c>
       <c r="D12" t="n">
         <v>16.41514</v>
       </c>
       <c r="E12" t="n">
-        <v>16.62076</v>
+        <v>16.60597</v>
       </c>
       <c r="F12" t="n">
         <v>42.78833</v>
@@ -745,10 +745,10 @@
         <v>16.87593</v>
       </c>
       <c r="D13" t="n">
+        <v>16.53013</v>
+      </c>
+      <c r="E13" t="n">
         <v>16.76438</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.53013</v>
       </c>
       <c r="F13" t="n">
         <v>42.99326</v>
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.79486</v>
+        <v>16.94823</v>
       </c>
       <c r="D19" t="n">
         <v>16.42452</v>
       </c>
       <c r="E19" t="n">
-        <v>16.94823</v>
+        <v>16.79486</v>
       </c>
       <c r="F19" t="n">
         <v>41.3149</v>
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.67725</v>
+        <v>16.71148</v>
       </c>
       <c r="D20" t="n">
         <v>16.65176</v>
       </c>
       <c r="E20" t="n">
-        <v>16.71148</v>
+        <v>16.67725</v>
       </c>
       <c r="F20" t="n">
         <v>42.4265</v>
